--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98796</v>
+        <v>98800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100963</v>
+        <v>100967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106402</v>
+        <v>106406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98811</v>
+        <v>98815</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98800</v>
+        <v>98802</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100967</v>
+        <v>100969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106406</v>
+        <v>106408</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98815</v>
+        <v>98817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98802</v>
+        <v>98812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100969</v>
+        <v>100979</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106408</v>
+        <v>106418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98817</v>
+        <v>98827</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98812</v>
+        <v>98816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100979</v>
+        <v>100983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106418</v>
+        <v>106422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98827</v>
+        <v>98831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98816</v>
+        <v>98819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100983</v>
+        <v>100986</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106422</v>
+        <v>106425</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98831</v>
+        <v>98834</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98819</v>
+        <v>98820</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100986</v>
+        <v>100987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106425</v>
+        <v>106426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98834</v>
+        <v>98835</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98820</v>
+        <v>98837</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>100987</v>
+        <v>101004</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106426</v>
+        <v>106443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98835</v>
+        <v>98852</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98853</v>
+        <v>98855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>129799948</v>
       </c>
       <c r="B3" t="n">
-        <v>101020</v>
+        <v>101022</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106459</v>
+        <v>106462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>129799932</v>
       </c>
       <c r="B5" t="n">
-        <v>98868</v>
+        <v>98870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 53126-2025 artfynd.xlsx
+++ b/artfynd/A 53126-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129799937</v>
       </c>
       <c r="B2" t="n">
-        <v>98855</v>
+        <v>99141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129799948</v>
+        <v>129799932</v>
       </c>
       <c r="B3" t="n">
-        <v>101022</v>
+        <v>99156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,34 +801,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219875</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Custer) Rchb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mösseberg - Plågerås 23. 5, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412520</v>
+        <v>412535</v>
       </c>
       <c r="R3" t="n">
-        <v>6453063</v>
+        <v>6453092</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,6 +881,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -895,7 +908,7 @@
         <v>129799915</v>
       </c>
       <c r="B4" t="n">
-        <v>106462</v>
+        <v>106812</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129799932</v>
+        <v>129799948</v>
       </c>
       <c r="B5" t="n">
-        <v>98870</v>
+        <v>101325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1005,46 +1018,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219875</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Mösseberg - Plågerås 23. 5, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>412535</v>
+        <v>412520</v>
       </c>
       <c r="R5" t="n">
-        <v>6453092</v>
+        <v>6453063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1085,7 +1086,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
